--- a/planilha_atualizada.xlsx
+++ b/planilha_atualizada.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RITM2442</t>
         </is>
       </c>
     </row>
